--- a/Result/profitability/1216.xlsx
+++ b/Result/profitability/1216.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>0.82</v>
+        <v>0.8625</v>
       </c>
       <c r="N2" t="n">
-        <v>32.2975</v>
+        <v>32.42124999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7500000000000001</v>
+        <v>0.8574999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>31.67</v>
+        <v>31.96625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.52</v>
       </c>
       <c r="M4" t="n">
-        <v>0.74625</v>
+        <v>0.80875</v>
       </c>
       <c r="N4" t="n">
-        <v>31.215</v>
+        <v>31.3175</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5875</v>
+        <v>0.6425</v>
       </c>
       <c r="N5" t="n">
-        <v>30.26125</v>
+        <v>30.28375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.535</v>
+        <v>0.5787500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>29.8275</v>
+        <v>29.88625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.78</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0.61125</v>
       </c>
       <c r="N7" t="n">
-        <v>29.515</v>
+        <v>29.79625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5025000000000001</v>
+        <v>0.535</v>
       </c>
       <c r="N8" t="n">
-        <v>29.44625</v>
+        <v>29.47125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.73</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4637500000000001</v>
+        <v>0.46375</v>
       </c>
       <c r="N11" t="n">
         <v>29.8275</v>
@@ -1899,7 +1899,7 @@
         <v>0.86</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5062500000000001</v>
+        <v>0.50625</v>
       </c>
       <c r="N12" t="n">
         <v>30.31</v>
@@ -2026,7 +2026,7 @@
         <v>0.24</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5812499999999999</v>
+        <v>0.58125</v>
       </c>
       <c r="N13" t="n">
         <v>30.1325</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>174921</v>
+      </c>
+      <c r="D75" t="n">
+        <v>115474</v>
+      </c>
+      <c r="E75" t="n">
+        <v>59447</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10257</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.86%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4263</v>
+      </c>
+      <c r="J75" t="n">
+        <v>14520</v>
+      </c>
+      <c r="K75" t="n">
+        <v>8006</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2260869565217392</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1999999999999957</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.005920663114268754</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4536082474226804</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1799999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.005325443786982298</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
